--- a/mltzao_unique_combos.xlsx
+++ b/mltzao_unique_combos.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="整机配置组合" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="去重配置组合" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'整机配置组合'!$A$1:$Q$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'去重配置组合'!$A$1:$P$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -450,17 +450,16 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
     <col width="35" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,7 +490,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CPU型号</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -501,24 +500,24 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>显卡(完整)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>内存规格</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>内存(完整)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>机箱</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>显卡(完整)</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>主板</t>
@@ -526,25 +525,20 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>内存(完整)</t>
+          <t>硬盘</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>硬盘</t>
+          <t>CPU散热</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CPU散热</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>电源</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>发货时效</t>
         </is>
@@ -582,24 +576,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>华硕 DUAL-RTX3050-O6G</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>MLOONG G003 Pro 黑色</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 5 5500</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>华硕 DUAL-RTX3050-O6G</t>
-        </is>
-      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>技嘉 A520M K V2</t>
@@ -607,25 +601,20 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
+          <t>九州风神 PF500（免费升 PF500X铜牌毁灭者）</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF500（免费升 PF500X铜牌毁灭者）</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -663,24 +652,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>华硕 DUAL-RTX3050-O6G</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MLOONG G003 Pro 黑色</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>华硕 DUAL-RTX3050-O6G</t>
-        </is>
-      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>技嘉 B760M H DDR4</t>
@@ -688,25 +677,20 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>Tt 钢影 400S</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Tt 钢影 400S</t>
+          <t>九州风神 PF500（免费升 PF500X铜牌毁灭者）</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF500（免费升 PF500X铜牌毁灭者）</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -744,24 +728,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>华硕 ATS-RX7650GRE-O8G</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>MLOONG G003 Pro 黑色</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 5 5600</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ATS-RX7650GRE-O8G</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>技嘉 A520M K V2</t>
@@ -769,25 +753,20 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -821,24 +800,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>盈通 RTX5050 8G 大地之神</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>MLOONG G003 Pro 黑色</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>盈通 RTX5050 8G 大地之神</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>华硕 PRIME B760M-F D4</t>
@@ -846,25 +825,20 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>Tt 钢影 400S</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Tt 钢影 400S</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF500（免费升 PF500X铜牌毁灭者）</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -898,24 +872,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 3060 GAMING OC 8G</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>MLOONG G003 Pro 黑色</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 5 5500X3D</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 3060 GAMING OC 8G</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>技嘉 B550M H ARGB</t>
@@ -923,25 +897,20 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -975,24 +944,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>MLOONG G003 Pro WH 白色</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>华硕 PRIME B760M-F D4</t>
@@ -1000,25 +969,20 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>Tt 钢影 400S</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Tt 钢影 400S</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1052,24 +1016,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 5 5500X3D</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>技嘉 B550M H ARGB</t>
@@ -1077,25 +1041,20 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1129,24 +1088,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-13400F</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>华硕 PRIME B760M-F D4</t>
@@ -1154,25 +1113,20 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1206,24 +1160,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>华硕 PRIME B760M-F D4</t>
@@ -1231,25 +1185,20 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1283,24 +1232,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>技嘉 B550M H ARGB</t>
@@ -1308,25 +1257,20 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1360,24 +1304,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>盈通 RTX5060Ti 8G 大地之神</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-13400F</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>盈通 RTX5060Ti 8G 大地之神</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>华硕 PRIME B760M-F D4</t>
@@ -1385,25 +1329,20 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
           <t>全汉（FSP）VIC BD 650W 铜牌电源</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1437,24 +1376,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>盈通 RTX5060Ti 8G 大地之神</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>8G DDR4 3200</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>盈通 RTX5060Ti 8G 大地之神</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>华硕 PRIME B760M-F D4</t>
@@ -1462,25 +1401,20 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
           <t>全汉（FSP）VIC BD 650W 铜牌电源</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1514,24 +1448,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>华硕 DUAL-RTX5060-O8G</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core Ultra 5 230F</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>华硕 DUAL-RTX5060-O8G</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>技嘉 B860M K</t>
@@ -1539,25 +1473,20 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1565,23 +1494,23 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>机械大师C24 标准版 蜡笔小新 9.9L （限时赠送 机械大师主机收纳背包 联系客服领取）</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>pro366084</t>
+          <t>diy859138</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>7992</v>
+        <v>8002</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1385179</v>
+        <v>1679751</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>AMD Ryzen 5 9600X</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1591,54 +1520,45 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8G DDR4 3200</t>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>机械大师C24 标准版 蜡笔小新 9.9L （限时赠送 机械大师主机收纳背包 联系客服领取）</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>铭瑄 MS-挑战者 H610ITX D4（免费赠送无线网卡，需联系客服领取）</t>
+          <t>铭瑄 MS-挑战者 B650M WIFI</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 黑色</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>利民 SGFX650-W 白色 金牌全模组SFX电源 ATX3.1</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PF600（免费升级PF650）</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1651,71 +1571,70 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>diy859138</t>
+          <t>diy865691</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8002</v>
+        <v>8052</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1679751</v>
+        <v>1677063</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>Intel Core Ultra 5 230F</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>华硕 DUAL-RTX5060TI-O8G</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 5 9600X</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>铭瑄 MS-挑战者 B650M WIFI</t>
+          <t>技嘉 B860M K</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>Crucial英睿达 美光E100 480GB</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>九州风神 玄冰400 ARGB</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
+          <t>全汉（FSP）VIC BD 650W 铜牌电源</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PF600（免费升级PF650）</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1723,76 +1642,71 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>华硕 彗星A01 白-印花集</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>diy865691</t>
+          <t>pro625055</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>8052</v>
+        <v>8355</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1677063</v>
+        <v>1519042</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 5 230F</t>
+          <t>Intel Core i5-13400F</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>华硕 PRIME-RTX5060-O8G</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>8G DDR4 3200</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 5 230F</t>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>华硕 DUAL-RTX5060TI-O8G</t>
+          <t>华硕 彗星A01 白-印花集</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B860M K</t>
+          <t>华硕 B760M-AYW WIFI D4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 480GB</t>
+          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 黑色</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰400 ARGB</t>
+          <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>全汉（FSP）VIC BD 650W 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -1804,23 +1718,23 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
+          <t>星璨 岚 白-粉色印花集 灯板款</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>pro639505</t>
+          <t>pro429490</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8123</v>
+        <v>8521</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1519042</v>
+        <v>1385179</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1830,50 +1744,45 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>华硕 ATS-RTX5060-O8G</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>8G DDR4 3200</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400F</t>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>七彩虹 iGame RTX 5060 Ultra W DUO OC 8GB</t>
+          <t>星璨 岚 白-粉色印花集 灯板款</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME B760M-F D4</t>
+          <t>华硕 B760M-AYW WIFI D4</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE240 V2 冰果240 白色</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 白色</t>
+          <t>九州风神 PF650</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>利民 SGFX650-W 白色 金牌全模组SFX电源 ATX3.1</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -1911,24 +1820,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>七彩虹 iGame RTX 5060 Ultra W OC 8GB</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>8G DDR4 3200</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>机械大师 IF25逻辑库 极地白 26.3L</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>七彩虹 iGame RTX 5060 Ultra W OC 8GB</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>技嘉 B550M H ARGB</t>
@@ -1936,25 +1845,20 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 白色</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 白色</t>
+          <t>利民 SGFX650 黑色 金牌全模组SFX电源 ATX3.1</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>利民 SGFX650 黑色 金牌全模组SFX电源 ATX3.1</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -1966,16 +1870,16 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era 印花集</t>
+          <t>华硕 彗星A01 白-吹雪联名款</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>pro205621</t>
+          <t>pro667017</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8580</v>
+        <v>8645</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1597455</v>
@@ -1992,50 +1896,45 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>华硕 DUAL-RTX5060TI-O8G</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>8G DDR4 3200</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>星纪元 X-Era 印花集</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13490F</t>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>华硕 DUAL-RTX5060TI-O8G</t>
+          <t>华硕 彗星A01 白-吹雪联名款</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME B760M-F D4</t>
+          <t>华硕 B760M-AYW WIFI D4</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 玄冰500 白色 ARGB</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 白色 ARGB</t>
+          <t>九州风神 PF650</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF650</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -2047,80 +1946,71 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>机械大师C24 标准版 极地白 9.9L（限时赠送 机械大师主机收纳背包+ 利民风扇一个   联系客服领取）</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>pro342034</t>
+          <t>diy205577</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>8692</v>
+        <v>8872</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1699076</v>
+        <v>1865111</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 5 225F</t>
+          <t>AMD Ryzen 5 9600X</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 Ti WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>机械大师C24 标准版 极地白 9.9L（限时赠送 机械大师主机收纳背包+ 利民风扇一个   联系客服领取）</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 5 225F</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>铭瑄 MS-Challenger H810ITX WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>Crucial英睿达 美光E100 1TB</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 CR1400EVO ARGB版白色款</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>利民 SGFX650-W 白色 金牌全模组SFX电源 ATX3.1</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>全汉（FSP）VIC BD 650W 铜牌电源</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2128,76 +2018,75 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>diy205577</t>
+          <t>pro158843</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>8872</v>
+        <v>8963</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1865111</v>
+        <v>1699076</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>Intel Core Ultra 5 225F</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>七彩虹 iGame RTX 5060 Ultra W DUO OC 8GB</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>MLOONG G005 黑色</t>
-        </is>
-      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>技嘉 RTX 5060 Ti WINDFORCE OC 8G</t>
+          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>技嘉 B860M K</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 1TB</t>
+          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 白色</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
+          <t>利民 SGFX650-W 白色 金牌全模组SFX电源 ATX3.1</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>全汉（FSP）VIC BD 650W 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2205,19 +2094,19 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>机械大师C28极地白 17.9L（注意：装240水冷的同时，无法兼容ATX电源）</t>
+          <t>华硕 海王星 黑-吹雪</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>pro195307</t>
+          <t>pro678965</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>9042</v>
+        <v>9360</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1579554</v>
+        <v>1520312</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -2226,27 +2115,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8G DDR4 3200</t>
+          <t>华硕 PRIME-RTX5060-O8G</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>机械大师C28极地白 17.9L（注意：装240水冷的同时，无法兼容ATX电源）</t>
+          <t>16G DDR4 3600</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400F</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5060 Ti 8G GAMING TRIO OC</t>
+          <t>华硕 海王星 黑-吹雪</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2256,25 +2145,20 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 黑色</t>
+          <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF650</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -2286,19 +2170,19 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>华硕 海王星 黑-吹雪</t>
+          <t>S980龙卷风 黑-金克丝</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>pro678965</t>
+          <t>pro520255</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>9360</v>
+        <v>9600</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1520312</v>
+        <v>1580824</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -2307,27 +2191,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>华硕 DUAL-RTX5060TI-O8G</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3600</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>华硕 海王星 黑-吹雪</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400F</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME-RTX5060-O8G</t>
+          <t>S980龙卷风 黑-金克丝</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2337,25 +2221,20 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
+          <t>九州风神 PF650</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF600（免费升级PF650）</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -2367,19 +2246,19 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>未知玩家 幻翼 LCD副屏 雪域白</t>
+          <t>乔思伯 X400 深空灰</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>pro614682</t>
+          <t>pro171264</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>9443</v>
+        <v>9621</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1830121</v>
+        <v>1769609</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -2388,55 +2267,50 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8G DDR4 3200</t>
+          <t>华硕 PRIME-RTX5060-O8G</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>未知玩家 幻翼 LCD副屏 雪域白</t>
+          <t>16G DDR4 3200</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3200 内存条</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>华硕 DUAL-RTX5060TI-O8G</t>
+          <t>乔思伯 X400 深空灰</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW WIFI D4</t>
+          <t>华硕 PRIME B760M-F D4</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PF650</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ750G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -2448,76 +2322,71 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S980龙卷风 黑-金克丝</t>
+          <t>名龙堂 M.star 龙头 开放式机箱 黑晶版</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>pro520255</t>
+          <t>pro869477</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>9600</v>
+        <v>9641</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1580824</v>
+        <v>1386449</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>技嘉 RTX 5060 WINDFORCE OC 8G</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3600</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>S980龙卷风 黑-金克丝</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400F</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>华硕 DUAL-RTX5060TI-O8G</t>
+          <t>名龙堂 M.star 龙头 开放式机箱 黑晶版</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME B760M-F D4</t>
+          <t>华硕 B760M-AYW WIFI D4</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE240 V2 冰果240 黑色</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
+          <t>九州风神 PF600（免费升级PF650）</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF650</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -2529,48 +2398,48 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-金克斯JINX</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>pro722835</t>
+          <t>diy325114</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9600</v>
+        <v>9751</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1386449</v>
+        <v>1849121</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16G DDR4 3600</t>
+          <t>技嘉 RTX 5060 Ti WINDFORCE OC 8G</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-金克斯JINX</t>
+          <t>16G DDR4 3200</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3200 内存条</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>华硕 TX-RTX5060-O8G</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2580,29 +2449,20 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
+          <t>Crucial英睿达 美光E100 1TB</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF600（免费升级PF650）</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PL750D 铜牌电源</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2610,48 +2470,48 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 深空灰</t>
+          <t>星纪元 X-Era Plus 印花集限定版</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>pro171264</t>
+          <t>pro165477</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>9621</v>
+        <v>9821</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1769609</v>
+        <v>1016446</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>Intel Core i5-13400F</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16G DDR4 3200</t>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 深空灰</t>
+          <t>8G DDR4 3200</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME-RTX5060-O8G</t>
+          <t>星纪元 X-Era Plus 印花集限定版</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2661,29 +2521,20 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3200 内存条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF650</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PQ750G WH 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2691,76 +2542,71 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>星纪元 X-Era 印花集</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>diy325114</t>
+          <t>pro427463</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9751</v>
+        <v>9950</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1849121</v>
+        <v>1766181</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>Intel Core i5-13600KF</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16G DDR4 3200</t>
+          <t>华硕 TX-RTX5060-O8G</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>16G DDR4 3600</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>技嘉 RTX 5060 Ti WINDFORCE OC 8G</t>
+          <t>星纪元 X-Era 印花集</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW WIFI D4</t>
+          <t>华硕 PRIME B760M-F D4</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3200 内存条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 1TB</t>
+          <t>九州风神 玄冰500 ARGB</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr"/>
+          <t>九州风神 PF600（免费升级PF650）</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2768,16 +2614,16 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-金克斯JINX</t>
+          <t>星璨 岚 白-印花集</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>pro922350</t>
+          <t>pro166302</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>9800</v>
+        <v>10012</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1577504</v>
@@ -2794,50 +2640,45 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>华硕 ATS-RX7650GRE-O8G</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-金克斯JINX</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 7500F</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>华硕 ATS-RX7650GRE-O8G</t>
+          <t>星璨 岚 白-印花集</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>华硕 B650M-AYW WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE240 V2 冰果240 黑色</t>
+          <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -2849,76 +2690,71 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era 印花集</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>pro427463</t>
+          <t>diy802818</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>9950</v>
+        <v>10802</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1766181</v>
+        <v>1445170</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13600KF</t>
+          <t>AMD Ryzen 7 9700X</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16G DDR4 3600</t>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era 印花集</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-13600KF</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>华硕 TX-RTX5060-O8G</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME B760M-F D4</t>
+          <t>华硕 B650M-AYW WIFI</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>九州风神 玄冰500 ARGB</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF600（免费升级PF650）</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr"/>
+          <t>九州风神 PL750D 铜牌电源</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2926,76 +2762,71 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-印花集</t>
+          <t>华硕 彗星A01 白-吹雪联名款</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>pro166302</t>
+          <t>pro543809</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>10012</v>
+        <v>10905</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1577504</v>
+        <v>1830121</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 7500F</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>RX 7650 GRE</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>华硕 DUAL-RTX5060TI-O8G</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-印花集</t>
+          <t>8G DDR4 3200</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 7500F</t>
+          <t>十铨（Team）火神Z DDR4 8GB 3200 白色</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>华硕 ATS-RX7650GRE-O8G</t>
+          <t>华硕 彗星A01 白-吹雪联名款</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>华硕 B760M-AYW WIFI D4</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 PRIME 大师 360ARGB CPU水冷散热器 白色</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>华硕 ROG-STRIX-850P-GAMING 均流线</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -3007,19 +2838,19 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>机械大师C+MAX樱花粉 20.5L</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>diy802818</t>
+          <t>pro554758</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>10802</v>
+        <v>11452</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1445170</v>
+        <v>1847659</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -3028,55 +2859,54 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RX 7650 GRE</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>华硕 ATS-RX7650GRE-O8G</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
+          <t>机械大师C+MAX樱花粉 20.5L</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>华硕 B650M-AYW WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE240 V2 冰果240 白色</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>利民 SGFX850-W 白色 金牌全模组SFX电源 ATX3.1</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3084,48 +2914,48 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-印花集</t>
+          <t>华硕 海王星 黑-火影鸣人</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>pro530444</t>
+          <t>pro523732</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>11412</v>
+        <v>11570</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1785599</v>
+        <v>1577504</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>AMD Ryzen 5 7500F</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RX 7650 GRE</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>华硕 ATS-RX7650GRE-O8G</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-印花集</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>华硕 ATS-RTX5060-O8G</t>
+          <t>华硕 海王星 黑-火影鸣人</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3135,25 +2965,20 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 白色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 PRIME 大师360 ARGB LCD一体式水冷散热器 屏幕款 黑色</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>华硕 ROG-STRIX-850P-GAMING 均流线</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -3165,48 +2990,48 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>机械大师C+MAX樱花粉 20.5L</t>
+          <t>星璨大岚屏显版 白-剑来</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>pro554758</t>
+          <t>pro777851</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>11452</v>
+        <v>11852</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1847659</v>
+        <v>1785599</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>AMD Ryzen 5 9600X</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>RX 7650 GRE</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5060 8G GAMING TRIO OC</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>机械大师C+MAX樱花粉 20.5L</t>
-        </is>
-      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 白色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>华硕 ATS-RX7650GRE-O8G</t>
+          <t>星璨大岚屏显版 白-剑来</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3216,25 +3041,20 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE240 V2 冰果240 白色</t>
+          <t>九州风神 PQ750G WH 金牌全模电源</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>利民 SGFX850-W 白色 金牌全模组SFX电源 ATX3.1</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -3272,24 +3092,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>机械大师 IF15逻辑库 典雅黑 16.5升 （限时赠送 机械大师主机收纳背包 联系客服领取）</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
-        </is>
-      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>铭瑄 MS 终结者 B760BKB D5 WIFI 显卡背插 b760itx主板</t>
@@ -3297,25 +3117,20 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE240 V2 冰果240 黑色</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE240 V2 冰果240 黑色</t>
+          <t>九州风神 PF650</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PF650</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -3327,23 +3142,23 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-绫波丽</t>
+          <t>S980龙卷风 白-卡比 灯板款</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ip994020</t>
+          <t>ip110089</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>11931</v>
+        <v>12101</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1964927</v>
+        <v>1425170</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>AMD Ryzen 7 9700X</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3353,50 +3168,45 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 8GB</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>华硕 彗星A01 黑-绫波丽</t>
-        </is>
-      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>华硕 DUAL-RTX5060TI-O8G</t>
+          <t>S980龙卷风 白-卡比 灯板款</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW PRO WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>十铨 火神 DDR5 6000 32GB（16Gx2）C28 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>瓦尔基里（VALKYRIE）B360 VK</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -3408,23 +3218,23 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>S980龙卷风 黑-鬼刀</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ip187427</t>
+          <t>diy376618</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>12001</v>
+        <v>12151</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1425170</v>
+        <v>1420819</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3434,54 +3244,45 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>S980龙卷风 黑-鬼刀</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5060 Ti X2B 8GB</t>
+          <t>MLOONG G005 黑色</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>华硕 B760M-AYW PRO WIFI</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>Crucial英睿达 美光E100 1TB</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里（VALKYRIE）B360 VK</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+      <c r="P38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3489,23 +3290,23 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>diy376618</t>
+          <t>pro816024</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>12151</v>
+        <v>12323</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1420819</v>
+        <v>1283003</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>AMD Ryzen 5 9600X</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3515,50 +3316,49 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G005 黑色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
+          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW PRO WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 美光E100 1TB</t>
+          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 黑色</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>利民 SGFX650 黑色 金牌全模组SFX电源 ATX3.1</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3566,16 +3366,16 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-间谍过家家</t>
+          <t>星璨大岚屏显版 白-剑来</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ip443076</t>
+          <t>ip505523</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>12312</v>
+        <v>12662</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1657643</v>
@@ -3592,22 +3392,22 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5060 8G GAMING TRIO OC</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>星璨 岚 白-间谍过家家</t>
-        </is>
-      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>芝奇 皇家戟 32GB（16G*2）DDR5 6000 银色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5060 8G GAMING TRIO OC</t>
+          <t>星璨大岚屏显版 白-剑来</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3617,25 +3417,20 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>芝奇 皇家戟 32GB（16G*2）DDR5 6000 银色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>Tt 途腾 旋风V240 白色</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Tt 途腾 旋风V240 白色</t>
+          <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -3647,80 +3442,71 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
+          <t>星璨 岚 屏幕款 白-MLOONG BLD红白</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>pro816024</t>
+          <t>pro485705</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>12323</v>
+        <v>12882</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1283003</v>
+        <v>2335166</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>Intel Core Ultra 7 270K Plus</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>微星 RTX 5060 8G GAMING TRIO OC</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>机械大师 IF25逻辑库 极地白 26.3L</t>
+          <t>48G DDR5 6000</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
+          <t>星璨 岚 屏幕款 白-MLOONG BLD红白</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>技嘉 B860M K</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>机械大师 凛冬 KK135 双塔逆重力 风冷散热器 黑色</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>利民 SGFX650 黑色 金牌全模组SFX电源 ATX3.1</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PQ750G WH 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3728,76 +3514,75 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 屏幕款 白-MLOONG BLD红白</t>
+          <t>VISION 白色 + 定制屏幕</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>pro485705</t>
+          <t>pro486715</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>12882</v>
+        <v>12902</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2335166</v>
+        <v>2083692</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>AMD Ryzen 5 9600X</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>AX电竞叛客 RTX 5070 X2W</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 屏幕款 白-MLOONG BLD红白</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5060 8G GAMING TRIO OC</t>
+          <t>VISION 白色 + 定制屏幕</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B860M K</t>
+          <t>华硕 B650M-AYW WIFI</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PQ750G WH 金牌全模电源</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PQ750G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr"/>
+          <t>72小时内发货</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3805,23 +3590,23 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>VISION 白色 + 定制屏幕</t>
+          <t>星纪元 X-Era 印花集</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>pro486715</t>
+          <t>pro951136</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>12902</v>
+        <v>13000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2083692</v>
+        <v>2068972</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3831,52 +3616,47 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>VISION 白色 + 定制屏幕</t>
+          <t>16G DDR4 3600</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 9600X</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5070 X2W</t>
+          <t>星纪元 X-Era 印花集</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>华硕 B650M-AYW WIFI</t>
+          <t>微星 PRO B760M-A DDR4 II</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE240 V2 冰果240 黑色</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PQ750G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>72小时内发货</t>
+          <t>7天内发货</t>
         </is>
       </c>
     </row>
@@ -3886,19 +3666,19 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era 印花集</t>
+          <t>MLOONG G007 黑色</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>pro951136</t>
+          <t>diy376613</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>13000</v>
+        <v>13481</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2068972</v>
+        <v>2222508</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3912,54 +3692,45 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16G DDR4 3600</t>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era 印花集</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+          <t>MLOONG G007 黑色</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>微星 PRO B760M-A DDR4 II</t>
+          <t>华硕 B760M-AYW PRO WIFI</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>美商海盗船 复仇者LPX 16GB DDR4 3600 内存条</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE240 V2 冰果240 黑色</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+      <c r="P44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3967,19 +3738,19 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G007 黑色</t>
+          <t>星璨 岚 屏幕款 白-印花集</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>diy376613</t>
+          <t>pro661991</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>13481</v>
+        <v>13494</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2222508</v>
+        <v>1401819</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3988,27 +3759,27 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G007 黑色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+          <t>星璨 岚 屏幕款 白-印花集</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -4018,25 +3789,24 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>九州风神 PQ750G WH 金牌全模电源</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4070,24 +3840,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>联力 LIANLI 锋翼V100 黑色</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i7-14700KF</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>AX电竞叛客 RTX 5060 Ti X2B 16GB</t>
-        </is>
-      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t>微星 Z790 GAMING PLUS WIFI</t>
@@ -4095,25 +3865,20 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PQ750G 金牌全模电源</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4147,24 +3912,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>MLOONG G005 黑色</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 7 9700X</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
-        </is>
-      </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
           <t>华硕 B850M AYW GAMING WIFI</t>
@@ -4172,25 +3937,20 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4224,24 +3984,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5060 Ti 16G GAMING TRIO OC WHITE</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
           <t>48G DDR5 6000</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>VK03 屏幕款 白-印花集白</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core Ultra 5 250K Plus</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>微星 RTX 5060 Ti 16G GAMING TRIO OC WHITE</t>
-        </is>
-      </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
           <t>技嘉 B860M K</t>
@@ -4249,25 +4009,20 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>钛钽 TCOMAS LG600 360 ARGB 白色</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>钛钽 TCOMAS LG600 360 ARGB 白色</t>
+          <t>九州风神 PQ750G WH 金牌全模电源</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ750G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -4305,24 +4060,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>MLOONG G007 黑色</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
-        </is>
-      </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
           <t>华硕 B650M-AYW WIFI</t>
@@ -4330,25 +4085,20 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
-      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4382,24 +4132,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 7200</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>华硕 A01彗星MATX 黑色</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core Ultra 7 265KF</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
-        </is>
-      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>微星 Z890 GAMING PLUS WIFI6E</t>
@@ -4407,25 +4157,20 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PL750D 铜牌电源</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4433,23 +4178,23 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era Plus 印花集限定版</t>
+          <t>酷冷至尊 TD500 MESH V2 白色</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>pro305828</t>
+          <t>diy815060</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>14412</v>
+        <v>15332</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2202508</v>
+        <v>2426825</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>Intel Core i7-14700KF</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4459,50 +4204,45 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>星纪元 X-Era Plus 印花集限定版</t>
+          <t>32G DDR5 7200</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+          <t>酷冷至尊 TD500 MESH V2 白色</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW PRO WIFI</t>
+          <t>微星 Z790 GAMING PLUS WIFI</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr"/>
+          <t>九州风神 PQ750G 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4510,23 +4250,23 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>酷冷至尊 TD500 MESH V2 白色</t>
+          <t>乔思伯 X400 银白色</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>diy815060</t>
+          <t>pro887183</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>15332</v>
+        <v>15452</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2426825</v>
+        <v>2206075</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -4536,50 +4276,49 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 7200</t>
+          <t>AX电竞叛客 RTX 5070 X2W</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>酷冷至尊 TD500 MESH V2 白色</t>
+          <t>48G DDR5 6000</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
+          <t>乔思伯 X400 银白色</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>微星 Z790 GAMING PLUS WIFI</t>
+          <t>华硕 TUF GAMING B760M-PLUS WIFI II</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PQ850G WH 金牌全模电源</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PQ750G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4587,23 +4326,23 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 银白色</t>
+          <t>联力 LIANLI 锋翼V100 黑色</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>pro887183</t>
+          <t>diy211887</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>15452</v>
+        <v>15972</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2206075</v>
+        <v>2270523</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4613,54 +4352,45 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>微星 RTX 5070 12G SHADOW 2X OC</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 银白色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5070 X2W</t>
+          <t>联力 LIANLI 锋翼V100 黑色</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B760M-PLUS WIFI II</t>
+          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PQ750G 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4668,16 +4398,16 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>机械大师C34PRO月光银 30.6L</t>
+          <t>机械大师C+MAX极地白 20.5L</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>pro946531</t>
+          <t>pro117527</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>15801</v>
+        <v>16381</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>2268606</v>
@@ -4694,50 +4424,45 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
           <t>16G DDR4 3200</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>机械大师C34PRO月光银 30.6L</t>
-        </is>
-      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>美商海盗船 复仇者LPX 16GB DDR4 3200 内存条</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>机械大师C+MAX极地白 20.5L</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME B760M-F D4</t>
+          <t>华硕 B760M-AYW WIFI D4</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR4 16G 3200 内存条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>Tt 途腾 旋风V240 白色</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>利民 SGFX850-W 白色 金牌全模组SFX电源 ATX3.1</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -4749,23 +4474,23 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-金克斯JINX</t>
+          <t>乔思伯 BO400</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ip941505</t>
+          <t>pro985343</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>15951</v>
+        <v>16522</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>2250523</v>
+        <v>2454213</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4775,50 +4500,45 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
+          <t>华硕 PRIME-RTX5070-O12G</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>华硕 彗星A01 黑-金克斯JINX</t>
-        </is>
-      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME-RTX5070-O12G</t>
+          <t>乔思伯 BO400</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>华硕 TUF GAMING B860M-PLUS WIFI</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>十铨 火神 DDR5 6000 32GB（16Gx2）C28 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>九州风神 PQ850G 金牌全模电源</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -4830,19 +4550,19 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>名龙堂 M.star 龙头 开放式机箱 氢蓝版</t>
+          <t>MLOONG G007 黑色</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>pro126006</t>
+          <t>diy626739</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>16132</v>
+        <v>16852</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2403412</v>
+        <v>2423601</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -4856,54 +4576,45 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>名龙堂 M.star 龙头 开放式机箱 氢蓝版</t>
+          <t>32G DDR5 7200</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>MLOONG G007 黑色</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>微星 MAG B760M MORTAR WIFI II</t>
+          <t>华硕 B760M-AYW PRO WIFI</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE240 V2 冰果240 白色</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PQ750G 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -4911,23 +4622,23 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 BO400</t>
+          <t>弹药库 黑-ROG灯板款无界</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>pro985343</t>
+          <t>pro325092</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>16522</v>
+        <v>17231</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2454213</v>
+        <v>2202508</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4937,50 +4648,45 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
+          <t>华硕 PRIME-RTX5070-O12G</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>乔思伯 BO400</t>
-        </is>
-      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME-RTX5070-O12G</t>
+          <t>弹药库 黑-ROG灯板款无界</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B860M-PLUS WIFI</t>
+          <t>华硕 TUF GAMING B760M-PLUS WIFI II</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 PRIME 大师360 ARGB LCD一体式水冷散热器 屏幕款 黑色</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>华硕 ROG-STRIX-850P-GAMING 均流线</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -4992,23 +4698,23 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G007 黑色</t>
+          <t>华硕 A01彗星MATX 黑色</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>diy626739</t>
+          <t>diy164466</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>16852</v>
+        <v>17423</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>2423601</v>
+        <v>2278884</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>AMD Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -5018,50 +4724,45 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 7200</t>
+          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G007 黑色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
+          <t>华硕 A01彗星MATX 黑色</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW PRO WIFI</t>
+          <t>华硕 B850M AYW GAMING WIFI</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>Crucial英睿达 P310 1TB</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PQ750G 金牌全模电源</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5069,19 +4770,19 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>华硕 A01彗星MATX 黑色</t>
+          <t>星纪元 X-Era Plus 印花集限定版</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>diy164466</t>
+          <t>pro557962</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>17423</v>
+        <v>17771</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>2278884</v>
+        <v>2258884</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -5095,50 +4796,45 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>华硕 A01彗星MATX 黑色</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 7800X3D</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
+          <t>星纪元 X-Era Plus 印花集限定版</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>华硕 B850M AYW GAMING WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 P310 1TB</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ750G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr"/>
+          <t>九州风神 PL750D 铜牌电源</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5146,76 +4842,71 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-间谍过家家</t>
+          <t>星璨 岚 屏幕款 黑-JINX</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ip389837</t>
+          <t>pro825428</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>17572</v>
+        <v>17930</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>2403412</v>
+        <v>1449834</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>七彩虹 iGame RTX 5070 Ultra OC 12GB</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 白-间谍过家家</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i5-14600KF</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>星璨 岚 屏幕款 黑-JINX</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW PRO WIFI</t>
+          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>十铨 火神 DDR5 6000 32GB（16Gx2）C28 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>爱国者 星璨魔方 点阵像素屏 360水冷 黑色</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里（VALKYRIE）B360W VK</t>
+          <t>九州风神 PQ750G 金牌全模电源</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -5227,23 +4918,23 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>酷冷至尊 MF400 全铝机箱 MESH银色</t>
+          <t>名龙堂 M.star 龙头 开放式机箱 黑晶版</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>pro379397</t>
+          <t>pro215295</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>17742</v>
+        <v>17991</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2258884</v>
+        <v>2403412</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5253,50 +4944,45 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>酷冷至尊 MF400 全铝机箱 MESH银色</t>
-        </is>
-      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 7800X3D</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>名龙堂 M.star 龙头 开放式机箱 黑晶版</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>华硕 TUF GAMING B760M-PLUS WIFI II</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE240 V2 冰果240 黑色</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PQ850G 金牌全模电源</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -5308,80 +4994,71 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 屏幕款 黑-JINX</t>
+          <t>MLOONG G007 黑色</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>pro825428</t>
+          <t>diy577382</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>17930</v>
+        <v>18102</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1449834</v>
+        <v>2830785</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core Ultra 7 270K Plus</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5070 Ti</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>星璨 岚 屏幕款 黑-JINX</t>
+          <t>32G DDR5 7200</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>七彩虹 iGame RTX 5070 Ultra OC 12GB</t>
+          <t>MLOONG G007 黑色</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
+          <t>微星 Z890 GAMING PLUS WIFI6E</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>爱国者 星璨魔方 点阵像素屏 360水冷 黑色</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ750G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PQ850G 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5389,23 +5066,23 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MLOONG G007 黑色</t>
+          <t>瓦尔基里（VALKYRIE）VK03 BLACK 黑色</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>diy577382</t>
+          <t>diy584213</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>18102</v>
+        <v>18242</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>2830785</v>
+        <v>2607729</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>Intel Core i7-14700KF</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5415,50 +5092,49 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 7200</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>MLOONG G007 黑色</t>
-        </is>
-      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
+          <t>瓦尔基里（VALKYRIE）VK03 BLACK 黑色</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>微星 Z890 GAMING PLUS WIFI6E</t>
+          <t>微星 Z790 GAMING PLUS WIFI</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>瓦尔基里（VALKYRIE）GLA360 BLACK VK</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>九州风神 PQ750G 金牌全模电源</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5471,18 +5147,18 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>diy584213</t>
+          <t>diy600223</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>18242</v>
+        <v>19442</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2607729</v>
+        <v>2454994</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -5492,50 +5168,45 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 7200</t>
+          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
+          <t>48G DDR5 6000</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 黑色</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
           <t>瓦尔基里（VALKYRIE）VK03 BLACK 黑色</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i7-14700KF</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
-        </is>
-      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>微星 Z790 GAMING PLUS WIFI</t>
+          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>瓦尔基里（VALKYRIE）GLA360 BLACK VK</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里（VALKYRIE）GLA360 BLACK VK</t>
+          <t>九州风神 PQ750G 金牌全模电源</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ750G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -5547,23 +5218,23 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>机械大师C34PRO月光银 30.6L</t>
+          <t>华硕 彗星A01 黑-爱死机霓虹</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>pro131797</t>
+          <t>pro110948</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>18602</v>
+        <v>19911</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2607540</v>
+        <v>2426763</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>AMD Ryzen 7 9700X</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5573,50 +5244,45 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
+          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>机械大师C34PRO月光银 30.6L</t>
-        </is>
-      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>华硕 彗星A01 黑-爱死机霓虹</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>华硕 B760M-AYW PRO WIFI</t>
+          <t>技嘉 B650M GAMING WIFI</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 PRIME 大师360 ARGB LCD一体式水冷散热器 屏幕款 黑色</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -5628,23 +5294,23 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>VISION 白色 + 定制屏幕</t>
+          <t>乔思伯 X400 深空灰</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>pro748196</t>
+          <t>diy788130</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>19349</v>
+        <v>21022</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2830596</v>
+        <v>2214304</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>AMD Ryzen 7 9850X3D</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -5654,54 +5320,45 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>VISION 白色 + 定制屏幕</t>
-        </is>
-      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>威刚 XPG 龙耀D500G DDR5 6000 32GB（16G*2）C26 黑色</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>乔思伯 X400 深空灰</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B860M-PLUS WIFI</t>
+          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PL750D 铜牌电源</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+          <t>九州风神 PQ850G 金牌全模电源</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5709,23 +5366,23 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里（VALKYRIE）VK03 BLACK 黑色</t>
+          <t>乔思伯 X400 白色</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>diy600223</t>
+          <t>pro488019</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>19442</v>
+        <v>21542</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2454994</v>
+        <v>2903314</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core Ultra 7 270K Plus</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5735,50 +5392,45 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
+          <t>七彩虹 iGame RTX 5070 Ti Vulcan W OC 16GB</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
           <t>48G DDR5 6000</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>瓦尔基里（VALKYRIE）VK03 BLACK 黑色</t>
-        </is>
-      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G VENTUS 3X OC</t>
+          <t>乔思伯 X400 白色</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
+          <t>华硕 TUF GAMING B860M-PLUS WIFI</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 黑色</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>钛钽 TCOMAS LA300 360 ARGB 白色</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里（VALKYRIE）GLA360 BLACK VK</t>
+          <t>九州风神 PQ850G 金牌全模电源</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ750G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -5790,80 +5442,71 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>未知玩家 幻翼 LCD副屏 星空黑</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>pro899278</t>
+          <t>diy347965</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>19903</v>
+        <v>21622</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2451427</v>
+        <v>2820887</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core i7-14700KF</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>微星 RTX 5080 16G VENTUS 3X OC PLUS</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>未知玩家 幻翼 LCD副屏 星空黑</t>
+          <t>48G DDR5 6000</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 黑色</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
+          <t>微星 Z790 GAMING PLUS WIFI</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 黑色</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
           <t>九州风神 PQ850G 金牌全模电源</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
-        </is>
-      </c>
+      <c r="P68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5871,76 +5514,71 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-爱死机霓虹</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>pro110948</t>
+          <t>diy220193</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>19911</v>
+        <v>22042</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2426763</v>
+        <v>3109716</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>Intel Core Ultra 7 270K Plus</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>微星 RTX 5080 16G VENTUS 3X OC PLUS</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>华硕 彗星A01 黑-爱死机霓虹</t>
+          <t>32G DDR5 7200</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9700X</t>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>技嘉 B650M GAMING WIFI</t>
+          <t>微星 Z890 GAMING PLUS WIFI6E</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LT360 VISION 黑色</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>华硕 PRIME 大师360 ARGB LCD一体式水冷散热器 屏幕款 黑色</t>
+          <t>九州风神 PQ850G 金牌全模电源</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -5952,76 +5590,71 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SSUPD 星舰 Xhuttle 机箱 白色（免费赠送3把风扇）</t>
+          <t>华硕 TUF GAMING GT302 装备库 白色</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>pro475055</t>
+          <t>pro117050</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>19963</v>
+        <v>23632</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2834163</v>
+        <v>3062029</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>Intel Core Ultra 9 285K</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>技嘉 RTX 5080 WINDFORCE OC SFF 16G</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>SSUPD 星舰 Xhuttle 机箱 白色（免费赠送3把风扇）</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>七彩虹 iGame RTX 5070 Ti Ultra W OC SFF 16GB</t>
+          <t>华硕 TUF GAMING GT302 装备库 白色</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B860M-PLUS WIFI</t>
+          <t>华硕 Z890 AYW GAMING WIFI W</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>钛钽 TCOMAS LA300 360 ARGB 白色</t>
+          <t>九州风神 PQ1000P WH 白金牌全模电源</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6033,48 +5666,48 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 深空灰</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>diy788130</t>
+          <t>diy330348</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>21022</v>
+        <v>23642</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2214304</v>
+        <v>2460235</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9850X3D</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
+          <t>微星 RTX 5080 16G VENTUS 3X OC PLUS</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>乔思伯 X400 深空灰</t>
-        </is>
-      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9850X3D</t>
+          <t>威刚 XPG 龙耀D500G DDR5 6000 32GB（16G*2）C26 黑色</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -6084,25 +5717,24 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>威刚 XPG 龙耀D500G DDR5 6000 32GB（16G*2）C26 黑色</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LT360 VISION 黑色</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>九州风神 PQ850G 金牌全模电源</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6110,76 +5742,75 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
+          <t>弹药库 白-ROG灯板款无界</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>diy347965</t>
+          <t>pro422962</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>21622</v>
+        <v>23791</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2820887</v>
+        <v>2451427</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070 Ti</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i7-14700KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5080 16G VENTUS 3X OC PLUS</t>
+          <t>弹药库 白-ROG灯板款无界</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>微星 Z790 GAMING PLUS WIFI</t>
+          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 天选 TX360 ARGB 一体式CPU水冷散热器 白色 天秀款</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>华硕 天选TX 850W 金牌全模组电源</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr"/>
+          <t>7天内发货</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6187,76 +5818,71 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 银白色</t>
+          <t>VISION 黑色 + 定制屏幕</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>pro525519</t>
+          <t>pro907652</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>21991</v>
+        <v>25287</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2979966</v>
+        <v>2607540</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>Intel Core i7-14700KF</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070 Ti</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>16G DDR5 6000</t>
+          <t>微星 RTX 5070 Ti 16G GAMING TRIO OC PLUS</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>乔思伯 X400 银白色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>技嘉 RTX 5080 WINDFORCE OC SFF 16G</t>
+          <t>VISION 黑色 + 定制屏幕</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>华硕 Z790-AYW OC WIFI</t>
+          <t>华硕 ROG STRIX Z790-A GAMING WIFI S 吹雪</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>TRYX（创氪星系）PANORAMA SE ARGB 360 黑色</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 黑色</t>
+          <t>海韵（SEASONIC）FOCUS GX1000</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ1000P 白金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6268,19 +5894,19 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
+          <t>创世神 黑-JINX</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>diy220193</t>
+          <t>pro670222</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>22042</v>
+        <v>25744</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>3109716</v>
+        <v>2830596</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -6289,55 +5915,50 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070 Ti</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 7200</t>
+          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 270K Plus</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5080 16G VENTUS 3X OC PLUS</t>
+          <t>创世神 黑-JINX</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>微星 Z890 GAMING PLUS WIFI6E</t>
+          <t>华硕 TUF GAMING Z890-PLUS WIFI</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
+          <t>华硕 PRIME 大师360 ARGB LCD一体式水冷散热器 屏幕款 黑色</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LT360 VISION 黑色</t>
+          <t>华硕 ROG-STRIX-850P-GAMING 均流线</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6349,23 +5970,23 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>追风者 EVOLV X2 Matrix 视界之窗 像素版</t>
+          <t>联力 LIANLI 包豪斯O11D EVO全视版 白色</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>pro677444</t>
+          <t>diy690360</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>23131</v>
+        <v>26492</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2664774</v>
+        <v>3057684</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core i9-14900KF</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6375,50 +5996,45 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
+          <t>七彩虹 iGame RTX 5080 Ultra W OC 16GB</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
           <t>48G DDR5 6000</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>追风者 EVOLV X2 Matrix 视界之窗 像素版</t>
-        </is>
-      </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>AX电竞叛客 RTX 5080 X3W 16GB</t>
+          <t>联力 LIANLI 包豪斯O11D EVO全视版 白色</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B850M-PLUS WIFI7 W</t>
+          <t>华硕 ROG STRIX Z790-A GAMING WIFI S 吹雪</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>钛钽 TCOMAS SJ-A090 360 ARGB 白色</t>
+          <t>海韵（SEASONIC）FOCUS GX1000</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6430,76 +6046,71 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING GT302 装备库 白色</t>
+          <t>ROG太阳神 白-吹雪联名</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>pro117050</t>
+          <t>pro264420</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23632</v>
+        <v>27437</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>3062029</v>
+        <v>2403412</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 9 285K</t>
+          <t>Intel Core i5-14600KF</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070 Ti</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
+          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>华硕 TUF GAMING GT302 装备库 白色</t>
-        </is>
-      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 9 285K</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>技嘉 RTX 5080 WINDFORCE OC SFF 16G</t>
+          <t>ROG太阳神 白-吹雪联名</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>华硕 Z890 AYW GAMING WIFI W</t>
+          <t>华硕 B760M-AYW PRO WIFI</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME 白色</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>华硕 ROG THOR 雷神3代 1200W</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ1000P WH 白金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6511,23 +6122,23 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 白色</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>diy330348</t>
+          <t>diy574738</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>23642</v>
+        <v>27792</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2460235</v>
+        <v>2771925</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>AMD Ryzen 7 9850X3D</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6537,50 +6148,45 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>七彩虹 iGame RTX 5080 Ultra W OC 16GB</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 黑色</t>
+          <t>48G DDR5 6000</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5080 16G VENTUS 3X OC PLUS</t>
+          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 白色</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING B850M-PLUS WIFI7</t>
+          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>威刚 XPG 龙耀D500G DDR5 6000 32GB（16G*2）C26 黑色</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
+          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LT360 VISION 黑色</t>
+          <t>华硕 ROG-STRIX-1000P-GAMING 吹雪 均流线</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6592,23 +6198,23 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>VK03 屏幕款 白-fate</t>
+          <t>VISION 白色 + 定制屏幕</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>pro552381</t>
+          <t>pro330075</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>24952</v>
+        <v>29437</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2979966</v>
+        <v>2669774</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -6618,50 +6224,45 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>七彩虹 iGame RTX 5080 Ultra W OC 16GB</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>VK03 屏幕款 白-fate</t>
+          <t>48G DDR5 6000</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>微星 RTX 5080 16G VANGUARD SOC LAUNCH EDITION</t>
+          <t>VISION 白色 + 定制屏幕</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG STRIX Z790-A GAMING WIFI S 吹雪</t>
+          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>TRYX（创氪星系）PANORAMA SE ARGB 360 白色</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PQ1000P WH 白金牌全模电源</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ850G WH 金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6673,19 +6274,19 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11D EVO全视版 白色</t>
+          <t>ROG太阳神 白-高达</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>diy690360</t>
+          <t>pro181395</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>26492</v>
+        <v>30387</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>3057684</v>
+        <v>2770186</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -6694,27 +6295,27 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070 Ti</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11D EVO全视版 白色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>七彩虹 iGame RTX 5080 Ultra W OC 16GB</t>
+          <t>ROG太阳神 白-高达</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -6724,25 +6325,20 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME 白色</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
+          <t>华硕 ROG THOR 雷神3代 1200W</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>海韵（SEASONIC）FOCUS GX1000</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6754,23 +6350,23 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 白色</t>
+          <t>创世神 黑-黑金ROG</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>diy574738</t>
+          <t>pro768139</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>27792</v>
+        <v>35388</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2771925</v>
+        <v>2979966</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9850X3D</t>
+          <t>Intel Core i9-14900KF</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -6780,50 +6376,45 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>华硕 ROG-ASTRAL-RTX5080-O16G-GAMING</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>联力 LIANLI 包豪斯O11 VISION COMPACT 白色</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9850X3D</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>七彩虹 iGame RTX 5080 Ultra W OC 16GB</t>
+          <t>创世神 黑-黑金ROG</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
+          <t>华硕 Z790-AYW OC WIFI</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
+          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-STRIX-1000P-GAMING 吹雪 均流线</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6835,19 +6426,19 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ROG太阳神 白-高达</t>
+          <t>ROG太阳神 白-吹雪联名</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>pro181395</t>
+          <t>pro176398</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>30387</v>
+        <v>37586</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2770186</v>
+        <v>2979966</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -6856,27 +6447,27 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>华硕 ROG-ASTRAL-RTX5080-O16G-GAMING</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>ROG太阳神 白-高达</t>
+          <t>16G DDR5 6000</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF-RTX5070TI-O16G-GAMING</t>
+          <t>ROG太阳神 白-吹雪联名</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -6886,25 +6477,20 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME 白色</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME 白色</t>
+          <t>华硕 ROG THOR 雷神3代 1200W</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG THOR 雷神3代 1200W</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -6937,29 +6523,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5090 D</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
+          <t>七彩虹 iGame RTX 5090 D v2 Vulcan W OC 24GB</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
           <t>48G DDR5 6000</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>联力 LIANLI 包豪斯O11D EVO全视版 白色</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i9-14900KF</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>七彩虹 iGame RTX 5090 D v2 Vulcan W OC 24GB</t>
-        </is>
-      </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
           <t>华硕 ROG STRIX Z790-A GAMING WIFI S 吹雪</t>
@@ -6967,25 +6553,20 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>三星（SAMSUNG）9100 PRO 2TB PCIe5.0*4固态硬盘</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>三星（SAMSUNG）9100 PRO 2TB PCIe5.0*4固态硬盘</t>
+          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
+          <t>九州风神 PQ1200P WH 白金牌全模电源</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ1200P WH 白金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -7023,24 +6604,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
           <t>16G DDR5 6000</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>VISION 白色 + 定制屏幕</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i9-14900KF</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
-        </is>
-      </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
           <t>华硕 Z790-AYW WIFI W II</t>
@@ -7048,25 +6629,20 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>GEIL金邦 DDR5 16G 6000 黑色马甲条</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>瓦尔基里 VALKYRIE V360 MERLIN VK 水冷散热器</t>
+          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -7078,19 +6654,19 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>弹药库 白-高达独角兽</t>
+          <t>华硕 TUF GAMING GT302 装备库 白色</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>pro844131</t>
+          <t>pro358472</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>53953</v>
+        <v>54732</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>3671199</v>
+        <v>3761081</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -7104,50 +6680,45 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>弹药库 白-高达独角兽</t>
-        </is>
-      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+          <t>华硕 TUF GAMING GT302 装备库 白色</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>华硕 Z790-AYW WIFI W II</t>
+          <t>华硕 ROG STRIX Z790-A GAMING WIFI S 吹雪</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Crucial英睿达 DDR5 Pro 32GB（16G*2）6000</t>
+          <t>WD_BLACK SN8100 2TB 固态硬盘</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>九州风神 LE360 V2 冰果360 白色</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME 白色</t>
+          <t>华硕 ROG THOR 雷神3代 1200W</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -7159,23 +6730,23 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>VISION 白色 + 定制屏幕</t>
+          <t>HYTE Y70TI 鱼缸 触摸2.5K副屏版 白色（免费赠送显卡竖装PCIE4.0满血延长线及支架）</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>pro578786</t>
+          <t>pro150909</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>54232</v>
+        <v>55281</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>3352171</v>
+        <v>3740170</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core i9-14900KF</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -7185,50 +6756,45 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6000</t>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>VISION 白色 + 定制屏幕</t>
+          <t>32G DDR5 6400</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>芝奇 幻锋戟 32GB（16G*2）DDR5 6400 科技银</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+          <t>HYTE Y70TI 鱼缸 触摸2.5K副屏版 白色（免费赠送显卡竖装PCIE4.0满血延长线及支架）</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
+          <t>华硕 Z790-AYW OC WIFI</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
+          <t>利民 WV 360 UB ARGB 奇幻视界 裸眼3D曲面屏 水冷散热器 白色</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>九州风神 LE360 V2 冰果360 白色</t>
+          <t>九州风神 PQ1200P WH 白金牌全模电源</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG THOR 雷神3代 1200W</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -7245,18 +6811,18 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>pro150909</t>
+          <t>pro686308</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>55281</v>
+        <v>56681</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>3740170</v>
+        <v>3424889</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900KF</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -7266,50 +6832,45 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 6400</t>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
+          <t>48G DDR5 6000</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
           <t>HYTE Y70TI 鱼缸 触摸2.5K副屏版 白色（免费赠送显卡竖装PCIE4.0满血延长线及支架）</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>Intel Core i9-14900KF</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
-        </is>
-      </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>华硕 Z790-AYW OC WIFI</t>
+          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>芝奇 幻锋戟 32GB（16G*2）DDR5 6400 科技银</t>
+          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
+          <t>利民 WV 360 UB ARGB 奇幻视界 裸眼3D曲面屏 水冷散热器 白色</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>利民 WV 360 UB ARGB 奇幻视界 裸眼3D曲面屏 水冷散热器 白色</t>
+          <t>九州风神 PQ1200P WH 白金牌全模电源</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ1200P WH 白金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -7321,23 +6882,23 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>HYTE Y70TI 鱼缸 触摸2.5K副屏版 白色（免费赠送显卡竖装PCIE4.0满血延长线及支架）</t>
+          <t>华硕 TUF GAMING GT502 弹药库 无界版</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>pro686308</t>
+          <t>diy261569</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>56681</v>
+        <v>57392</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>3424889</v>
+        <v>3803182</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>Intel Core Ultra 9 285K</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7347,50 +6908,45 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>48G DDR5 6000</t>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>HYTE Y70TI 鱼缸 触摸2.5K副屏版 白色（免费赠送显卡竖装PCIE4.0满血延长线及支架）</t>
+          <t>32G DDR5 7200</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 9800X3D</t>
+          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+          <t>华硕 TUF GAMING GT502 弹药库 无界版</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG STRIX X870-A GAMING WIFI S</t>
+          <t>华硕 ROG STRIX Z890-A GAMING WIFI S 吹雪</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>佰维（BIWIN）时空行者DW100 48GB（24Gx2）6000 C28 白色</t>
+          <t>三星（SAMSUNG）9100 PRO 2TB PCIe5.0*4固态硬盘</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>WD_BLACK SN8100 1TB 固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>利民 WV 360 UB ARGB 奇幻视界 裸眼3D曲面屏 水冷散热器 白色</t>
+          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>九州风神 PQ1200P WH 白金牌全模电源</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>7天内发货</t>
         </is>
@@ -7402,23 +6958,23 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING GT502 弹药库 无界版</t>
+          <t>创世神 黑-五条悟</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>diy261569</t>
+          <t>pro977533</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>57392</v>
+        <v>59792</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>3803182</v>
+        <v>3352171</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 9 285K</t>
+          <t>AMD Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -7428,52 +6984,47 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>32G DDR5 7200</t>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>华硕 TUF GAMING GT502 弹药库 无界版</t>
+          <t>32G DDR5 6000</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 9 285K</t>
+          <t>芝奇 烈焰枪 32GB（16G*2）DDR5 6000 黑色（C28/EXPO）</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+          <t>创世神 黑-五条悟</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG STRIX Z890-A GAMING WIFI S 吹雪</t>
+          <t>华硕 TUF GAMING X870-PLUS WIFI</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>十铨 幻境 DDR5 32GB（16Gx2）7200 ARGB 黑色</t>
+          <t>WD_BLACK SN7100 1TB 固态硬盘</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>三星（SAMSUNG）9100 PRO 2TB PCIe5.0*4固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME</t>
+          <t>华硕 ROG THOR 雷神3代 1200W</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr">
-        <is>
-          <t>7天内发货</t>
+          <t>10天内发货</t>
         </is>
       </c>
     </row>
@@ -7509,24 +7060,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
+          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
           <t>32G DDR5 6000</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>威刚 XPG 龙耀D500G DDR5 6000 32GB（16G*2）C26 黑色</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>华硕 ROG GR701 HYPERION 创世神</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 9 9950X3D</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>华硕 ROG-ASTRAL-RTX5090-O32G-GAMING（海外版）</t>
-        </is>
-      </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
           <t>华硕 ROG STRIX X870E-E GAMING WIFI</t>
@@ -7534,32 +7085,27 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>威刚 XPG 龙耀D500G DDR5 6000 32GB（16G*2）C26 黑色</t>
+          <t>三星（SAMSUNG）9100 PRO 2TB PCIe5.0*4固态硬盘</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>三星（SAMSUNG）9100 PRO 2TB PCIe5.0*4固态硬盘</t>
+          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG RYUJIN 龙神3代 360 ARGB EXTREME</t>
+          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>华硕 ROG-STRIX-1200P-GAMING 白金雷鹰</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr">
-        <is>
           <t>7天内发货</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q89"/>
+  <autoFilter ref="A1:P89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>